--- a/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_4G.xlsx
+++ b/network_excel_transformer/output/2G3G4G_Cell Info_CELLS_4G.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:G238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Downlink EARFCN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>azimuth</t>
         </is>
       </c>
@@ -495,6 +501,9 @@
         <v>310</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -521,6 +530,9 @@
         <v>311</v>
       </c>
       <c r="F3" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -547,6 +559,9 @@
         <v>309</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -573,6 +588,9 @@
         <v>97</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -599,6 +617,9 @@
         <v>96</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -625,6 +646,9 @@
         <v>98</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -651,6 +675,9 @@
         <v>176</v>
       </c>
       <c r="F8" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -677,6 +704,9 @@
         <v>175</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -703,6 +733,9 @@
         <v>174</v>
       </c>
       <c r="F10" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -729,6 +762,9 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -755,6 +791,9 @@
         <v>121</v>
       </c>
       <c r="F12" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -781,6 +820,9 @@
         <v>285</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -807,6 +849,9 @@
         <v>298</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,6 +878,9 @@
         <v>297</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -859,6 +907,9 @@
         <v>299</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -885,6 +936,9 @@
         <v>293</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,6 +965,9 @@
         <v>292</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -937,6 +994,9 @@
         <v>291</v>
       </c>
       <c r="F19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -963,6 +1023,9 @@
         <v>293</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,6 +1052,9 @@
         <v>292</v>
       </c>
       <c r="F21" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1015,6 +1081,9 @@
         <v>291</v>
       </c>
       <c r="F22" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1041,6 +1110,9 @@
         <v>293</v>
       </c>
       <c r="F23" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1067,6 +1139,9 @@
         <v>292</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1093,6 +1168,9 @@
         <v>291</v>
       </c>
       <c r="F25" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1119,6 +1197,9 @@
         <v>211</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,6 +1226,9 @@
         <v>210</v>
       </c>
       <c r="F27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1171,6 +1255,9 @@
         <v>212</v>
       </c>
       <c r="F28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1197,6 +1284,9 @@
         <v>211</v>
       </c>
       <c r="F29" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1223,6 +1313,9 @@
         <v>210</v>
       </c>
       <c r="F30" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1249,6 +1342,9 @@
         <v>212</v>
       </c>
       <c r="F31" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1275,6 +1371,9 @@
         <v>211</v>
       </c>
       <c r="F32" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1301,6 +1400,9 @@
         <v>210</v>
       </c>
       <c r="F33" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1327,6 +1429,9 @@
         <v>212</v>
       </c>
       <c r="F34" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1353,6 +1458,9 @@
         <v>156</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1379,6 +1487,9 @@
         <v>154</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1405,6 +1516,9 @@
         <v>155</v>
       </c>
       <c r="F37" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G37" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1431,6 +1545,9 @@
         <v>156</v>
       </c>
       <c r="F38" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,6 +1574,9 @@
         <v>154</v>
       </c>
       <c r="F39" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G39" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1483,6 +1603,9 @@
         <v>155</v>
       </c>
       <c r="F40" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1509,6 +1632,9 @@
         <v>456</v>
       </c>
       <c r="F41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1535,6 +1661,9 @@
         <v>458</v>
       </c>
       <c r="F42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1561,6 +1690,9 @@
         <v>457</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1587,6 +1719,9 @@
         <v>456</v>
       </c>
       <c r="F44" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1613,6 +1748,9 @@
         <v>458</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1639,6 +1777,9 @@
         <v>457</v>
       </c>
       <c r="F46" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G46" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1665,6 +1806,9 @@
         <v>456</v>
       </c>
       <c r="F47" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1691,6 +1835,9 @@
         <v>458</v>
       </c>
       <c r="F48" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G48" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1717,6 +1864,9 @@
         <v>457</v>
       </c>
       <c r="F49" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G49" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1743,6 +1893,9 @@
         <v>171</v>
       </c>
       <c r="F50" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1769,6 +1922,9 @@
         <v>172</v>
       </c>
       <c r="F51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1795,6 +1951,9 @@
         <v>173</v>
       </c>
       <c r="F52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G52" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1821,6 +1980,9 @@
         <v>171</v>
       </c>
       <c r="F53" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G53" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,6 +2009,9 @@
         <v>172</v>
       </c>
       <c r="F54" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G54" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1873,6 +2038,9 @@
         <v>173</v>
       </c>
       <c r="F55" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G55" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1899,6 +2067,9 @@
         <v>444</v>
       </c>
       <c r="F56" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G56" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1925,6 +2096,9 @@
         <v>92</v>
       </c>
       <c r="F57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1951,6 +2125,9 @@
         <v>346</v>
       </c>
       <c r="F58" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1977,6 +2154,9 @@
         <v>444</v>
       </c>
       <c r="F59" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G59" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2003,6 +2183,9 @@
         <v>92</v>
       </c>
       <c r="F60" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G60" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2029,6 +2212,9 @@
         <v>346</v>
       </c>
       <c r="F61" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G61" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2055,6 +2241,9 @@
         <v>72</v>
       </c>
       <c r="F62" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2081,6 +2270,9 @@
         <v>28</v>
       </c>
       <c r="F63" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G63" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2107,6 +2299,9 @@
         <v>296</v>
       </c>
       <c r="F64" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2133,6 +2328,9 @@
         <v>120</v>
       </c>
       <c r="F65" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,6 +2357,9 @@
         <v>73</v>
       </c>
       <c r="F66" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G66" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2185,6 +2386,9 @@
         <v>89</v>
       </c>
       <c r="F67" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G67" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2211,6 +2415,9 @@
         <v>72</v>
       </c>
       <c r="F68" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G68" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2237,6 +2444,9 @@
         <v>74</v>
       </c>
       <c r="F69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G69" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2263,6 +2473,9 @@
         <v>73</v>
       </c>
       <c r="F70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G70" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2289,6 +2502,9 @@
         <v>72</v>
       </c>
       <c r="F71" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G71" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2315,6 +2531,9 @@
         <v>74</v>
       </c>
       <c r="F72" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G72" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2341,6 +2560,9 @@
         <v>73</v>
       </c>
       <c r="F73" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G73" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2367,6 +2589,9 @@
         <v>72</v>
       </c>
       <c r="F74" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G74" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,6 +2618,9 @@
         <v>74</v>
       </c>
       <c r="F75" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G75" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2419,6 +2647,9 @@
         <v>73</v>
       </c>
       <c r="F76" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2445,6 +2676,9 @@
         <v>459</v>
       </c>
       <c r="F77" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G77" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2471,6 +2705,9 @@
         <v>460</v>
       </c>
       <c r="F78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G78" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2497,6 +2734,9 @@
         <v>461</v>
       </c>
       <c r="F79" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G79" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2523,6 +2763,9 @@
         <v>459</v>
       </c>
       <c r="F80" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G80" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2549,6 +2792,9 @@
         <v>460</v>
       </c>
       <c r="F81" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G81" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2575,6 +2821,9 @@
         <v>461</v>
       </c>
       <c r="F82" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G82" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2601,6 +2850,9 @@
         <v>459</v>
       </c>
       <c r="F83" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G83" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2627,6 +2879,9 @@
         <v>460</v>
       </c>
       <c r="F84" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2653,6 +2908,9 @@
         <v>461</v>
       </c>
       <c r="F85" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G85" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2679,6 +2937,9 @@
         <v>459</v>
       </c>
       <c r="F86" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G86" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2705,6 +2966,9 @@
         <v>460</v>
       </c>
       <c r="F87" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G87" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2731,6 +2995,9 @@
         <v>461</v>
       </c>
       <c r="F88" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G88" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2757,6 +3024,9 @@
         <v>460</v>
       </c>
       <c r="F89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G89" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2783,6 +3053,9 @@
         <v>459</v>
       </c>
       <c r="F90" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G90" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2809,6 +3082,9 @@
         <v>461</v>
       </c>
       <c r="F91" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2835,6 +3111,9 @@
         <v>460</v>
       </c>
       <c r="F92" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G92" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2861,6 +3140,9 @@
         <v>459</v>
       </c>
       <c r="F93" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G93" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2887,6 +3169,9 @@
         <v>461</v>
       </c>
       <c r="F94" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G94" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2913,6 +3198,9 @@
         <v>460</v>
       </c>
       <c r="F95" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2939,6 +3227,9 @@
         <v>459</v>
       </c>
       <c r="F96" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G96" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2965,6 +3256,9 @@
         <v>461</v>
       </c>
       <c r="F97" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G97" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -2991,6 +3285,9 @@
         <v>460</v>
       </c>
       <c r="F98" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3017,6 +3314,9 @@
         <v>459</v>
       </c>
       <c r="F99" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G99" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3043,6 +3343,9 @@
         <v>461</v>
       </c>
       <c r="F100" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G100" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3069,6 +3372,9 @@
         <v>341</v>
       </c>
       <c r="F101" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3095,6 +3401,9 @@
         <v>339</v>
       </c>
       <c r="F102" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G102" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3121,6 +3430,9 @@
         <v>340</v>
       </c>
       <c r="F103" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G103" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3147,6 +3459,9 @@
         <v>341</v>
       </c>
       <c r="F104" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G104" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3173,6 +3488,9 @@
         <v>339</v>
       </c>
       <c r="F105" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G105" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3199,6 +3517,9 @@
         <v>340</v>
       </c>
       <c r="F106" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G106" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3225,6 +3546,9 @@
         <v>341</v>
       </c>
       <c r="F107" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G107" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3251,6 +3575,9 @@
         <v>339</v>
       </c>
       <c r="F108" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G108" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3277,6 +3604,9 @@
         <v>340</v>
       </c>
       <c r="F109" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G109" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3303,6 +3633,9 @@
         <v>341</v>
       </c>
       <c r="F110" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G110" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3329,6 +3662,9 @@
         <v>339</v>
       </c>
       <c r="F111" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G111" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3355,6 +3691,9 @@
         <v>340</v>
       </c>
       <c r="F112" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G112" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3381,6 +3720,9 @@
         <v>393</v>
       </c>
       <c r="F113" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G113" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3407,6 +3749,9 @@
         <v>395</v>
       </c>
       <c r="F114" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G114" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3433,6 +3778,9 @@
         <v>394</v>
       </c>
       <c r="F115" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G115" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3459,6 +3807,9 @@
         <v>393</v>
       </c>
       <c r="F116" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G116" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3485,6 +3836,9 @@
         <v>395</v>
       </c>
       <c r="F117" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G117" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3511,6 +3865,9 @@
         <v>394</v>
       </c>
       <c r="F118" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G118" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3537,6 +3894,9 @@
         <v>393</v>
       </c>
       <c r="F119" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G119" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3563,6 +3923,9 @@
         <v>395</v>
       </c>
       <c r="F120" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G120" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3589,6 +3952,9 @@
         <v>394</v>
       </c>
       <c r="F121" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G121" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3615,6 +3981,9 @@
         <v>393</v>
       </c>
       <c r="F122" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G122" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3641,6 +4010,9 @@
         <v>395</v>
       </c>
       <c r="F123" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G123" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3667,6 +4039,9 @@
         <v>394</v>
       </c>
       <c r="F124" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G124" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3693,6 +4068,9 @@
         <v>169</v>
       </c>
       <c r="F125" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G125" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3719,6 +4097,9 @@
         <v>170</v>
       </c>
       <c r="F126" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G126" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3745,6 +4126,9 @@
         <v>168</v>
       </c>
       <c r="F127" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G127" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3771,6 +4155,9 @@
         <v>169</v>
       </c>
       <c r="F128" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G128" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3797,6 +4184,9 @@
         <v>170</v>
       </c>
       <c r="F129" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G129" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3823,6 +4213,9 @@
         <v>168</v>
       </c>
       <c r="F130" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G130" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3849,6 +4242,9 @@
         <v>169</v>
       </c>
       <c r="F131" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G131" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3875,6 +4271,9 @@
         <v>170</v>
       </c>
       <c r="F132" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G132" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3901,6 +4300,9 @@
         <v>168</v>
       </c>
       <c r="F133" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G133" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -3927,6 +4329,9 @@
         <v>169</v>
       </c>
       <c r="F134" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G134" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3953,6 +4358,9 @@
         <v>170</v>
       </c>
       <c r="F135" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G135" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3979,6 +4387,9 @@
         <v>168</v>
       </c>
       <c r="F136" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G136" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4005,6 +4416,9 @@
         <v>250</v>
       </c>
       <c r="F137" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G137" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4031,6 +4445,9 @@
         <v>251</v>
       </c>
       <c r="F138" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G138" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4057,6 +4474,9 @@
         <v>249</v>
       </c>
       <c r="F139" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G139" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4083,6 +4503,9 @@
         <v>250</v>
       </c>
       <c r="F140" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G140" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4109,6 +4532,9 @@
         <v>251</v>
       </c>
       <c r="F141" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G141" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4135,6 +4561,9 @@
         <v>249</v>
       </c>
       <c r="F142" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G142" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4161,6 +4590,9 @@
         <v>250</v>
       </c>
       <c r="F143" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G143" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4187,6 +4619,9 @@
         <v>251</v>
       </c>
       <c r="F144" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G144" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4213,6 +4648,9 @@
         <v>249</v>
       </c>
       <c r="F145" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G145" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4239,6 +4677,9 @@
         <v>250</v>
       </c>
       <c r="F146" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G146" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4265,6 +4706,9 @@
         <v>251</v>
       </c>
       <c r="F147" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G147" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4291,6 +4735,9 @@
         <v>249</v>
       </c>
       <c r="F148" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G148" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4317,6 +4764,9 @@
         <v>341</v>
       </c>
       <c r="F149" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G149" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4343,6 +4793,9 @@
         <v>339</v>
       </c>
       <c r="F150" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G150" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4369,6 +4822,9 @@
         <v>340</v>
       </c>
       <c r="F151" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G151" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4395,6 +4851,9 @@
         <v>341</v>
       </c>
       <c r="F152" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G152" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4421,6 +4880,9 @@
         <v>339</v>
       </c>
       <c r="F153" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G153" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4447,6 +4909,9 @@
         <v>340</v>
       </c>
       <c r="F154" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G154" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4473,6 +4938,9 @@
         <v>69</v>
       </c>
       <c r="F155" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G155" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4499,6 +4967,9 @@
         <v>70</v>
       </c>
       <c r="F156" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G156" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4525,6 +4996,9 @@
         <v>71</v>
       </c>
       <c r="F157" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G157" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4551,6 +5025,9 @@
         <v>69</v>
       </c>
       <c r="F158" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G158" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4577,6 +5054,9 @@
         <v>70</v>
       </c>
       <c r="F159" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G159" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4603,6 +5083,9 @@
         <v>71</v>
       </c>
       <c r="F160" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G160" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4629,6 +5112,9 @@
         <v>39</v>
       </c>
       <c r="F161" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G161" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4655,6 +5141,9 @@
         <v>41</v>
       </c>
       <c r="F162" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G162" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4681,6 +5170,9 @@
         <v>40</v>
       </c>
       <c r="F163" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G163" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4707,6 +5199,9 @@
         <v>39</v>
       </c>
       <c r="F164" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G164" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4733,6 +5228,9 @@
         <v>41</v>
       </c>
       <c r="F165" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G165" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4759,6 +5257,9 @@
         <v>40</v>
       </c>
       <c r="F166" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G166" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4785,6 +5286,9 @@
         <v>39</v>
       </c>
       <c r="F167" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G167" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4811,6 +5315,9 @@
         <v>41</v>
       </c>
       <c r="F168" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G168" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4837,6 +5344,9 @@
         <v>40</v>
       </c>
       <c r="F169" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G169" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4863,6 +5373,9 @@
         <v>39</v>
       </c>
       <c r="F170" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G170" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4889,6 +5402,9 @@
         <v>41</v>
       </c>
       <c r="F171" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G171" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4915,6 +5431,9 @@
         <v>40</v>
       </c>
       <c r="F172" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G172" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -4941,6 +5460,9 @@
         <v>252</v>
       </c>
       <c r="F173" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G173" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4967,6 +5489,9 @@
         <v>254</v>
       </c>
       <c r="F174" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G174" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4993,6 +5518,9 @@
         <v>253</v>
       </c>
       <c r="F175" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G175" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5019,6 +5547,9 @@
         <v>252</v>
       </c>
       <c r="F176" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G176" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5045,6 +5576,9 @@
         <v>254</v>
       </c>
       <c r="F177" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G177" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5071,6 +5605,9 @@
         <v>253</v>
       </c>
       <c r="F178" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G178" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5097,6 +5634,9 @@
         <v>252</v>
       </c>
       <c r="F179" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G179" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5123,6 +5663,9 @@
         <v>254</v>
       </c>
       <c r="F180" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G180" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5149,6 +5692,9 @@
         <v>253</v>
       </c>
       <c r="F181" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G181" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5175,6 +5721,9 @@
         <v>252</v>
       </c>
       <c r="F182" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G182" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5201,6 +5750,9 @@
         <v>254</v>
       </c>
       <c r="F183" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G183" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5227,6 +5779,9 @@
         <v>253</v>
       </c>
       <c r="F184" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G184" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5253,6 +5808,9 @@
         <v>43</v>
       </c>
       <c r="F185" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G185" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5279,6 +5837,9 @@
         <v>42</v>
       </c>
       <c r="F186" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G186" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5305,6 +5866,9 @@
         <v>44</v>
       </c>
       <c r="F187" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G187" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5331,6 +5895,9 @@
         <v>43</v>
       </c>
       <c r="F188" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G188" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5357,6 +5924,9 @@
         <v>42</v>
       </c>
       <c r="F189" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G189" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5383,6 +5953,9 @@
         <v>44</v>
       </c>
       <c r="F190" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G190" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5409,6 +5982,9 @@
         <v>43</v>
       </c>
       <c r="F191" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G191" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5435,6 +6011,9 @@
         <v>42</v>
       </c>
       <c r="F192" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G192" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5461,6 +6040,9 @@
         <v>44</v>
       </c>
       <c r="F193" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G193" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5487,6 +6069,9 @@
         <v>43</v>
       </c>
       <c r="F194" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G194" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5513,6 +6098,9 @@
         <v>42</v>
       </c>
       <c r="F195" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G195" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5539,6 +6127,9 @@
         <v>44</v>
       </c>
       <c r="F196" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G196" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5565,6 +6156,9 @@
         <v>309</v>
       </c>
       <c r="F197" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G197" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5591,6 +6185,9 @@
         <v>310</v>
       </c>
       <c r="F198" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G198" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5617,6 +6214,9 @@
         <v>311</v>
       </c>
       <c r="F199" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G199" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5643,6 +6243,9 @@
         <v>309</v>
       </c>
       <c r="F200" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G200" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5669,6 +6272,9 @@
         <v>310</v>
       </c>
       <c r="F201" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G201" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5695,6 +6301,9 @@
         <v>311</v>
       </c>
       <c r="F202" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G202" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5721,6 +6330,9 @@
         <v>309</v>
       </c>
       <c r="F203" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G203" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5747,6 +6359,9 @@
         <v>310</v>
       </c>
       <c r="F204" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G204" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5773,6 +6388,9 @@
         <v>311</v>
       </c>
       <c r="F205" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G205" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5799,6 +6417,9 @@
         <v>309</v>
       </c>
       <c r="F206" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G206" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5825,6 +6446,9 @@
         <v>310</v>
       </c>
       <c r="F207" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G207" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5851,6 +6475,9 @@
         <v>311</v>
       </c>
       <c r="F208" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G208" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5877,6 +6504,9 @@
         <v>425</v>
       </c>
       <c r="F209" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G209" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5903,6 +6533,9 @@
         <v>139</v>
       </c>
       <c r="F210" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G210" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5929,6 +6562,9 @@
         <v>339</v>
       </c>
       <c r="F211" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G211" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -5955,6 +6591,9 @@
         <v>425</v>
       </c>
       <c r="F212" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G212" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5981,6 +6620,9 @@
         <v>139</v>
       </c>
       <c r="F213" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G213" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6007,6 +6649,9 @@
         <v>339</v>
       </c>
       <c r="F214" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G214" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6033,6 +6678,9 @@
         <v>425</v>
       </c>
       <c r="F215" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G215" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6059,6 +6707,9 @@
         <v>139</v>
       </c>
       <c r="F216" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G216" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6085,6 +6736,9 @@
         <v>339</v>
       </c>
       <c r="F217" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G217" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6111,6 +6765,9 @@
         <v>425</v>
       </c>
       <c r="F218" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G218" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6137,6 +6794,9 @@
         <v>139</v>
       </c>
       <c r="F219" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G219" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6163,6 +6823,9 @@
         <v>339</v>
       </c>
       <c r="F220" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G220" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6189,6 +6852,9 @@
         <v>185</v>
       </c>
       <c r="F221" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G221" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6215,6 +6881,9 @@
         <v>139</v>
       </c>
       <c r="F222" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G222" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6241,6 +6910,9 @@
         <v>471</v>
       </c>
       <c r="F223" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G223" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6267,6 +6939,9 @@
         <v>185</v>
       </c>
       <c r="F224" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G224" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6293,6 +6968,9 @@
         <v>139</v>
       </c>
       <c r="F225" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G225" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6319,6 +6997,9 @@
         <v>471</v>
       </c>
       <c r="F226" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G226" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6345,6 +7026,9 @@
         <v>185</v>
       </c>
       <c r="F227" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G227" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6371,6 +7055,9 @@
         <v>139</v>
       </c>
       <c r="F228" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G228" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6397,6 +7084,9 @@
         <v>471</v>
       </c>
       <c r="F229" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G229" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6423,6 +7113,9 @@
         <v>185</v>
       </c>
       <c r="F230" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G230" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6449,6 +7142,9 @@
         <v>139</v>
       </c>
       <c r="F231" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G231" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6475,6 +7171,9 @@
         <v>471</v>
       </c>
       <c r="F232" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G232" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6501,6 +7200,9 @@
         <v>281</v>
       </c>
       <c r="F233" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G233" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6527,6 +7229,9 @@
         <v>279</v>
       </c>
       <c r="F234" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G234" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6553,6 +7258,9 @@
         <v>280</v>
       </c>
       <c r="F235" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G235" s="2" t="n">
         <v>240</v>
       </c>
     </row>
@@ -6579,6 +7287,9 @@
         <v>281</v>
       </c>
       <c r="F236" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G236" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6605,6 +7316,9 @@
         <v>279</v>
       </c>
       <c r="F237" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G237" s="2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6631,6 +7345,9 @@
         <v>280</v>
       </c>
       <c r="F238" s="2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G238" s="2" t="n">
         <v>240</v>
       </c>
     </row>
